--- a/PerCom/6_Evaluation/E1_E2_results.xlsx
+++ b/PerCom/6_Evaluation/E1_E2_results.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -731,80 +731,78 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>이력에서 EQUIV 55 + 이력에서 DIVERGE 66 + 반례 재생 8</t>
+          <t>이력에서 EQUIV 55 + 이력에서 DIVERGE 67 + 반례 재생 8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  정답기가 JoI 를 실행 못함</t>
+          <t xml:space="preserve">  정답기와 어긋남</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>C24_003/llm: 미초기화 변수 + 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  정답기와 어긋남</t>
+          <t>관찰 가능한 차이가 있는 오류 쌍</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>관찰 가능한 차이가 있는 오류 쌍</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>75</v>
+          <t xml:space="preserve">  DIVERGE / EQUIV / 판정 없음</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>69 / 0 / 6</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DIVERGE / EQUIV / 판정 없음</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>69 / 0 / 6</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>E2 표 — Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>E2 표 — Coverage</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LLM 생성 후보 판정</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>38/38</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LLM 생성 후보 판정</t>
+          <t>직접 만든 쌍 판정</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>92/102</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -812,12 +810,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>직접 만든 쌍 판정</t>
+          <t>직접 만든 요구 전부 판정</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>92/102</t>
+          <t>18/20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -825,41 +823,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>직접 만든 요구 전부 판정</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>18/20</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>판정 없음: 반복·타이머 중첩 (시간 예산 초과)</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>판정 없음: 반복·타이머 중첩 (시간 예산 초과)</t>
+          <t>판정 없음: 사건 수에 따라 늘어나는 시한 (거절)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>판정 없음: 사건 수에 따라 늘어나는 시한 (거절)</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>E1-099</t>
         </is>
@@ -8612,12 +8597,12 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>정답기가 JoI 실행 못함 (미초기화 변수 + 1)</t>
+          <t>이력에서 차이 있음</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr"/>
